--- a/countries/cy/2020-2025.xlsx
+++ b/countries/cy/2020-2025.xlsx
@@ -86012,17 +86012,17 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -86041,13 +86041,13 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O436" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="R436" t="n">
-        <v>1.750861204855138</v>
+        <v>0.2918102008091897</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
@@ -86056,7 +86056,7 @@
       </c>
       <c r="U436" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
+          <t>SER_CY_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AA436" t="inlineStr">
@@ -86081,7 +86081,7 @@
       </c>
       <c r="AS436" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
+          <t>SER_CY_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT436" t="n">
@@ -86171,17 +86171,17 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
@@ -86200,19 +86200,19 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="O437" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
+          <t>SER_CY_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="V437" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
+          <t>SER_CY_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="W437" t="inlineStr">
@@ -86222,7 +86222,7 @@
       </c>
       <c r="X437" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="Y437" t="inlineStr">
@@ -86315,7 +86315,7 @@
       </c>
       <c r="AS437" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
+          <t>SER_CY_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT437" t="n">
@@ -86405,17 +86405,17 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K438" t="inlineStr">
@@ -86434,13 +86434,13 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O438" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R438" t="n">
-        <v>0</v>
+        <v>1.750861204855138</v>
       </c>
       <c r="S438" t="inlineStr">
         <is>
@@ -86449,7 +86449,7 @@
       </c>
       <c r="U438" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA438" t="inlineStr">
@@ -86474,7 +86474,7 @@
       </c>
       <c r="AS438" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT438" t="n">
@@ -86564,17 +86564,17 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K439" t="inlineStr">
@@ -86593,19 +86593,19 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O439" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="U439" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="V439" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="W439" t="inlineStr">
@@ -86615,7 +86615,7 @@
       </c>
       <c r="X439" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y439" t="inlineStr">
@@ -86708,7 +86708,7 @@
       </c>
       <c r="AS439" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+          <t>SER_CY_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT439" t="n">
@@ -86798,17 +86798,17 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
@@ -86827,13 +86827,13 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O440" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R440" t="n">
-        <v>0.8024780522252716</v>
+        <v>0</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
@@ -86842,7 +86842,7 @@
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+          <t>SER_CY_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AA440" t="inlineStr">
@@ -86867,7 +86867,7 @@
       </c>
       <c r="AS440" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+          <t>SER_CY_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT440" t="n">
@@ -86957,17 +86957,17 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K441" t="inlineStr">
@@ -86986,19 +86986,19 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O441" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U441" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+          <t>SER_CY_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="V441" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+          <t>SER_CY_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="W441" t="inlineStr">
@@ -87008,7 +87008,7 @@
       </c>
       <c r="X441" t="inlineStr">
         <is>
-          <t>Legionnaires' disease</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="Y441" t="inlineStr">
@@ -87101,7 +87101,7 @@
       </c>
       <c r="AS441" t="inlineStr">
         <is>
-          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+          <t>SER_CY_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT441" t="n">
@@ -87148,6 +87148,3936 @@
         </is>
       </c>
       <c r="BC441" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="R442" t="n">
+        <v>0</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO442" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP442" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ442" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT442" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU442" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV442" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW442" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX442" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY442" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA442" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB442" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC442" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>0</v>
+      </c>
+      <c r="O443" t="n">
+        <v>0</v>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB443" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC443" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD443" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE443" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF443" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI443" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ443" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK443" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM443" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN443" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ443" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU443" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV443" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW443" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX443" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY443" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA443" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB443" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC443" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>0</v>
+      </c>
+      <c r="O444" t="n">
+        <v>0</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_ECHI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO444" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP444" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ444" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS444" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_ECHI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT444" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU444" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV444" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW444" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX444" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY444" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA444" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB444" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC444" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>D045</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>包虫病</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N445" t="n">
+        <v>0</v>
+      </c>
+      <c r="O445" t="n">
+        <v>0</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_ECHI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_ECHI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>Echinococcosis</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD445" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE445" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF445" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI445" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ445" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK445" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM445" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN445" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO445" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP445" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ445" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS445" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_ECHI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT445" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU445" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV445" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW445" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX445" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY445" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA445" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB445" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC445" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>0</v>
+      </c>
+      <c r="O446" t="n">
+        <v>0</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0</v>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO446" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP446" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ446" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS446" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU446" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV446" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW446" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX446" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY446" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA446" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB446" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC446" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>D085</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>弓形体病</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>0</v>
+      </c>
+      <c r="O447" t="n">
+        <v>0</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>Toxoplasmosis, congenital</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB447" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC447" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD447" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE447" t="inlineStr">
+        <is>
+          <t>narrower</t>
+        </is>
+      </c>
+      <c r="AF447" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI447" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ447" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK447" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM447" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN447" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO447" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP447" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ447" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS447" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TOXO_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU447" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV447" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW447" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX447" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA447" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB447" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC447" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>78</v>
+      </c>
+      <c r="O448" t="n">
+        <v>78</v>
+      </c>
+      <c r="R448" t="n">
+        <v>5.690298915779199</v>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO448" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP448" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ448" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT448" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU448" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV448" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW448" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX448" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA448" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB448" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC448" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>78</v>
+      </c>
+      <c r="O449" t="n">
+        <v>78</v>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W449" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB449" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC449" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD449" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE449" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF449" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG449" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI449" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ449" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK449" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM449" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN449" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ449" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS449" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU449" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV449" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW449" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX449" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY449" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA449" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB449" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC449" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N450" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="R450" t="n">
+        <v>0</v>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO450" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP450" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ450" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS450" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT450" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU450" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV450" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW450" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX450" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA450" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB450" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC450" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>0</v>
+      </c>
+      <c r="O451" t="n">
+        <v>0</v>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z451" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB451" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC451" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD451" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE451" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF451" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG451" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH451" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI451" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ451" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK451" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM451" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN451" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO451" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP451" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ451" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS451" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT451" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU451" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV451" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW451" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX451" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY451" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA451" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB451" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC451" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>11</v>
+      </c>
+      <c r="O452" t="n">
+        <v>11</v>
+      </c>
+      <c r="R452" t="n">
+        <v>0.8024780522252716</v>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO452" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP452" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ452" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS452" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT452" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU452" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV452" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW452" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX452" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY452" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA452" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB452" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC452" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N453" t="n">
+        <v>11</v>
+      </c>
+      <c r="O453" t="n">
+        <v>11</v>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>Legionnaires' disease</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB453" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC453" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD453" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE453" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF453" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG453" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH453" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI453" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ453" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK453" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM453" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN453" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO453" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP453" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ453" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS453" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT453" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU453" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV453" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW453" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX453" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY453" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA453" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB453" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC453" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>3</v>
+      </c>
+      <c r="O454" t="n">
+        <v>3</v>
+      </c>
+      <c r="R454" t="n">
+        <v>0.2188576506068922</v>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO454" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP454" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ454" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS454" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT454" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU454" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV454" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW454" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX454" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY454" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA454" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB454" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC454" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N455" t="n">
+        <v>3</v>
+      </c>
+      <c r="O455" t="n">
+        <v>3</v>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA455" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB455" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC455" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD455" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE455" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF455" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG455" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH455" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI455" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ455" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK455" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM455" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN455" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO455" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP455" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ455" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS455" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT455" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU455" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV455" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW455" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX455" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY455" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA455" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB455" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC455" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N456" t="n">
+        <v>82</v>
+      </c>
+      <c r="O456" t="n">
+        <v>82</v>
+      </c>
+      <c r="R456" t="n">
+        <v>5.982109116588388</v>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO456" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP456" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ456" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS456" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT456" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU456" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV456" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW456" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX456" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY456" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA456" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB456" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC456" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N457" t="n">
+        <v>82</v>
+      </c>
+      <c r="O457" t="n">
+        <v>82</v>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB457" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC457" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD457" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE457" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF457" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG457" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH457" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI457" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ457" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK457" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM457" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN457" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO457" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP457" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ457" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS457" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT457" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU457" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV457" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW457" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX457" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY457" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA457" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB457" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC457" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N458" t="n">
+        <v>0</v>
+      </c>
+      <c r="O458" t="n">
+        <v>0</v>
+      </c>
+      <c r="R458" t="n">
+        <v>0</v>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO458" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP458" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ458" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS458" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT458" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU458" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV458" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW458" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX458" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY458" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA458" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB458" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC458" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N459" t="n">
+        <v>0</v>
+      </c>
+      <c r="O459" t="n">
+        <v>0</v>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W459" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>STEC/VTEC infection</t>
+        </is>
+      </c>
+      <c r="Y459" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB459" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC459" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD459" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE459" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF459" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG459" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH459" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI459" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ459" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK459" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM459" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN459" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO459" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP459" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ459" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS459" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT459" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU459" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV459" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW459" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX459" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY459" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA459" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB459" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC459" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N460" t="n">
+        <v>0</v>
+      </c>
+      <c r="O460" t="n">
+        <v>0</v>
+      </c>
+      <c r="R460" t="n">
+        <v>0</v>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO460" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP460" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ460" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS460" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT460" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU460" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV460" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW460" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX460" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY460" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA460" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB460" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC460" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>cy</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N461" t="n">
+        <v>0</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0</v>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>SRC_CY_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z461" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB461" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC461" t="inlineStr">
+        <is>
+          <t>country:CY:national</t>
+        </is>
+      </c>
+      <c r="AD461" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE461" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF461" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG461" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH461" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI461" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ461" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK461" t="inlineStr">
+        <is>
+          <t>Cyprus annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM461" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN461" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO461" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP461" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ461" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS461" t="inlineStr">
+        <is>
+          <t>SER_CY_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT461" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU461" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV461" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW461" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX461" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY461" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA461" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Cyprus Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB461" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC461" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -87269,7 +91199,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -87279,7 +91209,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>440</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11">
@@ -87299,7 +91229,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13">
@@ -87331,7 +91261,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2684</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="16">
